--- a/simulacao_splendi.xlsx
+++ b/simulacao_splendi.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz DR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Delicci" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Natulce" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Skimil &amp; Skimoni" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A C Alves Lopes | Frutibom" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuários" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz DR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Delicci" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Natulce" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Skimil &amp; Skimoni" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A C Alves Lopes | Frutibom" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,25 @@
       <color rgb="00FFCC00"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +127,11 @@
         <fgColor rgb="00EEF4FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -136,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +219,21 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,6 +600,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>CONTROLE DE ACESSO — USUÁRIOS DO PORTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>⚠️  Mantenha este arquivo seguro. Não compartilhe as senhas por e-mail ou mensagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Usuário (login)</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Nome / Cliente</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Aba da Planilha</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Senha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>delicci</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>++ Delicci</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>++ Delicci</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>1Yd8@qyWp0Kx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>natulce</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>++ Natulce</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>++ Natulce</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>1UsAK@2LDQ2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>skimil</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>++ Skimil &amp; Skimoni</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>++ Skimil &amp; Skimoni</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>me$xyeX8u5ji</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>alves</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A C Alves Lopes | Frutibom</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>A C Alves Lopes | Frutibom</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>XoDXipsd39v$</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1841,7 +2027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2328,7 +2514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2733,367 +2919,6 @@
       <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A5:Q5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>SUGESTÃO DE PEDIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Cliente: ++ Skimil &amp; Skimoni Indústria Ltda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>CNPJ: 34.567.890/0001-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Endereço: Rod. BR-040, km 25 — Belo Horizonte/MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>⚠️  Confira os produtos abaixo e ajuste as quantidades antes de confirmar o pedido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>QNT</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Família</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Embalagem</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> kg </t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>Código para colar no sistema</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Preço/kg</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>Preço/embalagem</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Valor total </t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>Preço NET</t>
-        </is>
-      </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>ICMS%</t>
-        </is>
-      </c>
-      <c r="O8" s="15" t="inlineStr">
-        <is>
-          <t>PIS% + COFINS%</t>
-        </is>
-      </c>
-      <c r="P8" s="15" t="inlineStr">
-        <is>
-          <t>IPI%</t>
-        </is>
-      </c>
-      <c r="Q8" s="15" t="inlineStr">
-        <is>
-          <t>Desc Grupo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Açúcares</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Saco 25kg</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Especial</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="L9" s="20" t="n">
-        <v>2200</v>
-      </c>
-      <c r="M9" s="20" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N9" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O9" s="19" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="17" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Açúcares Liq.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>IBC 1000kg</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Açúcar Líquido 67 Brix</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>T° max 40°C</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>3200</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L10" s="23" t="n">
-        <v>16000</v>
-      </c>
-      <c r="M10" s="23" t="n">
-        <v>3.136</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Amidos</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>IBC 1000kg</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Xarope de Glicose 42DE</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>Viscosidade ok</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>3600</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L11" s="20" t="n">
-        <v>10800</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N11" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O11" s="19" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="17" t="inlineStr">
-        <is>
-          <t>Indústria</t>
         </is>
       </c>
     </row>
@@ -3149,6 +2974,367 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
+          <t>Cliente: ++ Skimil &amp; Skimoni Indústria Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>CNPJ: 34.567.890/0001-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Endereço: Rod. BR-040, km 25 — Belo Horizonte/MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>⚠️  Confira os produtos abaixo e ajuste as quantidades antes de confirmar o pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>QNT</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Família</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Embalagem</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> kg </t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Código para colar no sistema</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Preço/kg</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>Preço/embalagem</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valor total </t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Preço NET</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>ICMS%</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>PIS% + COFINS%</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>IPI%</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>Desc Grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Açúcares</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Saco 25kg</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Açúcar Cristal Especial</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t>Indústria</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Açúcares Liq.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>IBC 1000kg</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Açúcar Líquido 67 Brix</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>T° max 40°C</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>3200</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L10" s="23" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Indústria</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Amidos</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>IBC 1000kg</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Xarope de Glicose 42DE</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Viscosidade ok</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>10800</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O11" s="19" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t>Indústria</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A5:Q5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>SUGESTÃO DE PEDIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
           <t>Cliente: A C Alves Lopes — Frutibom Com. de Alimentos</t>
         </is>
       </c>

--- a/simulacao_splendi.xlsx
+++ b/simulacao_splendi.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuários" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz DR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Delicci" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Natulce" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Skimil &amp; Skimoni" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A C Alves Lopes | Frutibom" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz DR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Delicci" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Natulce" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="++ Skimil &amp; Skimoni" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A C Alves Lopes | Frutibom" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,25 +71,8 @@
       <color rgb="00FFCC00"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -127,11 +109,6 @@
         <fgColor rgb="00EEF4FB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -159,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,21 +196,6 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -600,154 +562,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>CONTROLE DE ACESSO — USUÁRIOS DO PORTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>⚠️  Mantenha este arquivo seguro. Não compartilhe as senhas por e-mail ou mensagem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Usuário (login)</t>
-        </is>
-      </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Nome / Cliente</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>Aba da Planilha</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Senha</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>delicci</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>++ Delicci</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>++ Delicci</t>
-        </is>
-      </c>
-      <c r="D4" s="27" t="inlineStr">
-        <is>
-          <t>1Yd8@qyWp0Kx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>natulce</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>++ Natulce</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>++ Natulce</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>1UsAK@2LDQ2r</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>skimil</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>++ Skimil &amp; Skimoni</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>++ Skimil &amp; Skimoni</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>me$xyeX8u5ji</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>alves</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>A C Alves Lopes | Frutibom</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>A C Alves Lopes | Frutibom</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>XoDXipsd39v$</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2027,7 +1841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2514,7 +2328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2919,6 +2733,367 @@
       <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A5:Q5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>SUGESTÃO DE PEDIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Cliente: ++ Skimil &amp; Skimoni Indústria Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>CNPJ: 34.567.890/0001-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Endereço: Rod. BR-040, km 25 — Belo Horizonte/MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>⚠️  Confira os produtos abaixo e ajuste as quantidades antes de confirmar o pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>QNT</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Família</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Embalagem</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> kg </t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Código para colar no sistema</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Preço/kg</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>Preço/embalagem</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valor total </t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Preço NET</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>ICMS%</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>PIS% + COFINS%</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>IPI%</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>Desc Grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Açúcares</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Saco 25kg</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Açúcar Cristal Especial</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t>Indústria</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Açúcares Liq.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>IBC 1000kg</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Açúcar Líquido 67 Brix</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>T° max 40°C</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>3200</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L10" s="23" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Indústria</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Amidos</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>IBC 1000kg</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Xarope de Glicose 42DE</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Viscosidade ok</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>10800</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O11" s="19" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t>Indústria</t>
         </is>
       </c>
     </row>
@@ -2974,367 +3149,6 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Cliente: ++ Skimil &amp; Skimoni Indústria Ltda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>CNPJ: 34.567.890/0001-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Endereço: Rod. BR-040, km 25 — Belo Horizonte/MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>⚠️  Confira os produtos abaixo e ajuste as quantidades antes de confirmar o pedido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>QNT</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Família</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Embalagem</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> kg </t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>Código para colar no sistema</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Preço/kg</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>Preço/embalagem</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Valor total </t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>Preço NET</t>
-        </is>
-      </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>ICMS%</t>
-        </is>
-      </c>
-      <c r="O8" s="15" t="inlineStr">
-        <is>
-          <t>PIS% + COFINS%</t>
-        </is>
-      </c>
-      <c r="P8" s="15" t="inlineStr">
-        <is>
-          <t>IPI%</t>
-        </is>
-      </c>
-      <c r="Q8" s="15" t="inlineStr">
-        <is>
-          <t>Desc Grupo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Açúcares</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Saco 25kg</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Açúcar Cristal Especial</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="L9" s="20" t="n">
-        <v>2200</v>
-      </c>
-      <c r="M9" s="20" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N9" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O9" s="19" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="17" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Açúcares Liq.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>IBC 1000kg</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Açúcar Líquido 67 Brix</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>T° max 40°C</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>3200</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L10" s="23" t="n">
-        <v>16000</v>
-      </c>
-      <c r="M10" s="23" t="n">
-        <v>3.136</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Amidos</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>IBC 1000kg</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Xarope de Glicose 42DE</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>Viscosidade ok</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>3600</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L11" s="20" t="n">
-        <v>10800</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N11" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O11" s="19" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="P11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="17" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A5:Q5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>SUGESTÃO DE PEDIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
           <t>Cliente: A C Alves Lopes — Frutibom Com. de Alimentos</t>
         </is>
       </c>
